--- a/stories/arbres/ATOM-LAN.MOT.001-03.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nassim est dans la cuisine. Papa pose un panier. Dedans, il y a une poire. Un raisin. Une chaussette. Un gant. Nassim touche la poire. Elle est lisse. Papa dit : on nomme. On classe. Les fruits ensemble. Les habits ensemble. La poire, c'est un fruit. Le raisin, c'est un fruit. Nassim les met ensemble. La chaussette, c'est un habit. Le gant, c'est un habit. Nassim les met ensemble. Papa dit : fruits, c'est une catégorie. Habits, c'est une catégorie. Nassim répète : catégorie. Il pose les fruits dans le panier. Il pose les habits sur la chaise.</t>
+          <t>Nassim est dans la cuisine. Papa pose un panier. Dedans, il y a une poire. Un raisin. Une chaussette. Un gant. Nassim touche la poire. Elle est lisse. On nomme. On classe. Les fruits ensemble. Les habits ensemble. La poire, c'est un fruit. Le raisin, c'est un fruit. Nassim les met ensemble. La chaussette, c'est un habit. Le gant, c'est un habit. Nassim les met ensemble. Fruits, c'est une catégorie. Habits, c'est une catégorie. Nassim répète : catégorie. Il pose les fruits dans le panier. Il pose les habits sur la chaise.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nassim est dans la cuisine. Papa pose un panier. Dedans, il y a une poire. Un raisin. Une chaussette. Un gant. Nassim touche la poire. Elle est lisse.
+papa|On nomme. On classe.
+narrateur|Les fruits ensemble. Les habits ensemble. La poire, c'est un fruit. Le raisin, c'est un fruit. Nassim les met ensemble. La chaussette, c'est un habit. Le gant, c'est un habit. Nassim les met ensemble.
+papa|Fruits, c'est une catégorie. Habits, c'est une catégorie.
+narrateur|Nassim répète : catégorie. Il pose les fruits dans le panier. Il pose les habits sur la chaise.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Nassim range poire et chaussette. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nassim a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Nassim croque la poire. Papa plie le gant.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-03.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Nassim répète : catégorie. Il pose les fruits dans le panier. Il pose les habits sur la chaise.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Nassim range poire et chaussette. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Nassim a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Nassim croque la poire. Papa plie le gant.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.MOT.001-03.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nassim classe fruits et habits</t>
+          <t>Le grain de raisin d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un grain de raisin roule jusqu'au sel. Le panier d'Amir mélange fruits et habits. Il nomme, il met ensemble, deux catégories.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nassim est dans la cuisine. Papa pose un panier. Dedans, il y a une poire. Un raisin. Une chaussette. Un gant. Nassim touche la poire. Elle est lisse. On nomme. On classe. Les fruits ensemble. Les habits ensemble. La poire, c'est un fruit. Le raisin, c'est un fruit. Nassim les met ensemble. La chaussette, c'est un habit. Le gant, c'est un habit. Nassim les met ensemble. Fruits, c'est une catégorie. Habits, c'est une catégorie. Nassim répète : catégorie. Il pose les fruits dans le panier. Il pose les habits sur la chaise.</t>
+          <t>Un grain de raisin roule, tout seul. Il s'arrête près du sel. Les volets laissent un filet d'or. L'horloge fait tic, puis tac. L'évier sent encore le savon. Une chaise racle un tout petit peu. Amir, tu as vu le grain ? Il a fait la course. Oui, papa. Il est tout rond. Le panier s'est mélangé, lui aussi. Viens voir. En ce moment, Amir monte sur la chaise. Le bois est lisse sous les mains. Papa pose le panier sur la table. Dedans, il y a une poire. Un raisin. Une chaussette. Un gant. La poire est lisse. Touche. Elle est froide. Amir touche la poire verte. Elle sent un peu l'herbe. Et le gant ? Il est jaune. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Amir prend la poire. Poire. C'est un fruit. Oui. Mets-la dans le panier. Amir met la poire dans le panier. Il prend la grappe de raisin. Les grains sont lisses et froids. Raisin. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Amir met le raisin avec la poire. Il prend la chaussette bleue. Elle est douce, un peu épaisse. Chaussette. C'est un habit. Oui. Pose-la sur la chaise. Amir pose la chaussette sur la chaise. Il prend le gant jaune. Le gant sent la laine. Gant. C'est un habit. Les habits ensemble. C'est une catégorie. Amir pose le gant sur la chaise. Catégorie. Fruits. Habits. Bravo, Amir. Tu as nommé. Tu as classé. Tu as mis ensemble. C'est du bon travail. Tu as fini de ranger le panier ? Oui, papa. Le panier a les fruits. La chaise a les habits. Le grain près du sel attend encore. On le met avec le raisin ? Oui. C'est un fruit. Amir pose le grain avec la grappe. L'horloge fait tac, tout calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,81 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Nassim est dans la cuisine. Papa pose un panier. Dedans, il y a une poire. Un raisin. Une chaussette. Un gant. Nassim touche la poire. Elle est lisse.
-papa|On nomme. On classe.
-narrateur|Les fruits ensemble. Les habits ensemble. La poire, c'est un fruit. Le raisin, c'est un fruit. Nassim les met ensemble. La chaussette, c'est un habit. Le gant, c'est un habit. Nassim les met ensemble.
-papa|Fruits, c'est une catégorie. Habits, c'est une catégorie.
-narrateur|Nassim répète : catégorie. Il pose les fruits dans le panier. Il pose les habits sur la chaise.</t>
+          <t>narrateur|Un grain de raisin roule, tout seul.
+narrateur|Il s'arrête près du sel.
+narrateur|Les volets laissent un filet d'or.
+narrateur|L'horloge fait tic, puis tac.
+narrateur|L'évier sent encore le savon.
+narrateur|Une chaise racle un tout petit peu.
+papa|Amir, tu as vu le grain ?
+papa|Il a fait la course.
+enfant-m|Oui, papa.
+enfant-m|Il est tout rond.
+papa|Le panier s'est mélangé, lui aussi.
+papa|Viens voir.
+narrateur|En ce moment, Amir monte sur la chaise.
+narrateur|Le bois est lisse sous les mains.
+narrateur|Papa pose le panier sur la table.
+narrateur|Dedans, il y a une poire.
+narrateur|Un raisin.
+narrateur|Une chaussette.
+narrateur|Un gant.
+enfant-m|La poire est lisse.
+papa|Touche.
+papa|Elle est froide.
+narrateur|Amir touche la poire verte.
+narrateur|Elle sent un peu l'herbe.
+enfant-m|Et le gant ?
+enfant-m|Il est jaune.
+papa|On nomme.
+papa|On classe.
+papa|Les fruits ensemble.
+papa|Les habits ensemble.
+narrateur|Amir prend la poire.
+enfant-m|Poire.
+enfant-m|C'est un fruit.
+papa|Oui.
+papa|Mets-la dans le panier.
+narrateur|Amir met la poire dans le panier.
+narrateur|Il prend la grappe de raisin.
+narrateur|Les grains sont lisses et froids.
+enfant-m|Raisin.
+enfant-m|C'est un fruit aussi.
+papa|Les fruits ensemble.
+papa|C'est une catégorie.
+narrateur|Amir met le raisin avec la poire.
+narrateur|Il prend la chaussette bleue.
+narrateur|Elle est douce, un peu épaisse.
+enfant-m|Chaussette.
+enfant-m|C'est un habit.
+papa|Oui.
+papa|Pose-la sur la chaise.
+narrateur|Amir pose la chaussette sur la chaise.
+narrateur|Il prend le gant jaune.
+narrateur|Le gant sent la laine.
+enfant-m|Gant.
+enfant-m|C'est un habit.
+papa|Les habits ensemble.
+papa|C'est une catégorie.
+narrateur|Amir pose le gant sur la chaise.
+enfant-m|Catégorie.
+enfant-m|Fruits.
+enfant-m|Habits.
+papa|Bravo, Amir.
+papa|Tu as nommé.
+papa|Tu as classé.
+papa|Tu as mis ensemble.
+papa|C'est du bon travail.
+papa|Tu as fini de ranger le panier ?
+enfant-m|Oui, papa.
+narrateur|Le panier a les fruits.
+narrateur|La chaise a les habits.
+narrateur|Le grain près du sel attend encore.
+papa|On le met avec le raisin ?
+enfant-m|Oui.
+enfant-m|C'est un fruit.
+narrateur|Amir pose le grain avec la grappe.
+narrateur|L'horloge fait tac, tout calme.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1426,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nassim range poire et chaussette. Que fait-il ?</t>
+          <t>Amir range poire et chaussette. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1582,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Nassim range poire et chaussette. Que fait-il ?</t>
+          <t>narrateur|Amir range poire et chaussette.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1611,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nassim a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits.</t>
+          <t>Amir a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo, Amir. C'est du bon travail. Les fruits sont où ? Dans le panier. Et les habits ? Sur la chaise. Le filet d'or a bougé sur la table. Le savon sent encore, tout près.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1755,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nassim a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits.</t>
+          <t>narrateur|Amir a nommé.
+narrateur|Il a classé.
+narrateur|Une catégorie pour les fruits.
+narrateur|Une catégorie pour les habits.
+papa|Tu as mis ensemble.
+papa|Bravo, Amir.
+papa|C'est du bon travail.
+papa|Les fruits sont où ?
+enfant-m|Dans le panier.
+papa|Et les habits ?
+enfant-m|Sur la chaise.
+narrateur|Le filet d'or a bougé sur la table.
+narrateur|Le savon sent encore, tout près.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1795,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nassim croque la poire. Papa plie le gant.</t>
+          <t>Amir croque la poire. Elle est juteuse, un peu ferme. Tu aimes ? Oui, papa. Papa plie le gant jaune. Il pose la chaussette sur le dossier. Les habits sont ensemble. Les fruits aussi. On laisse un grain pour plus tard ? Oui. Le raisin brille dans le panier. L'horloge continue, tout doux. Tu as classé, puis tu croques. C'était bien.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1836,7 +1931,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nassim croque la poire. Papa plie le gant.</t>
+          <t>narrateur|Amir croque la poire.
+narrateur|Elle est juteuse, un peu ferme.
+papa|Tu aimes ?
+enfant-m|Oui, papa.
+narrateur|Papa plie le gant jaune.
+narrateur|Il pose la chaussette sur le dossier.
+papa|Les habits sont ensemble.
+enfant-m|Les fruits aussi.
+papa|On laisse un grain pour plus tard ?
+enfant-m|Oui.
+narrateur|Le raisin brille dans le panier.
+narrateur|L'horloge continue, tout doux.
+papa|Tu as classé, puis tu croques.
+enfant-m|C'était bien.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1864,7 +1972,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai nommé. J'ai classé. Bravo. Tu as fait du bon travail. Le grain a rejoint sa grappe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2004,7 +2112,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai nommé.
+enfant-m|J'ai classé.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le grain a rejoint sa grappe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2026,7 +2139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2177,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-03.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un grain de raisin roule, tout seul. Il s'arrête près du sel. Les volets laissent un filet d'or. L'horloge fait tic, puis tac. L'évier sent encore le savon. Une chaise racle un tout petit peu. Amir, tu as vu le grain ? Il a fait la course. Oui, papa. Il est tout rond. Le panier s'est mélangé, lui aussi. Viens voir. En ce moment, Amir monte sur la chaise. Le bois est lisse sous les mains. Papa pose le panier sur la table. Dedans, il y a une poire. Un raisin. Une chaussette. Un gant. La poire est lisse. Touche. Elle est froide. Amir touche la poire verte. Elle sent un peu l'herbe. Et le gant ? Il est jaune. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Amir prend la poire. Poire. C'est un fruit. Oui. Mets-la dans le panier. Amir met la poire dans le panier. Il prend la grappe de raisin. Les grains sont lisses et froids. Raisin. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Amir met le raisin avec la poire. Il prend la chaussette bleue. Elle est douce, un peu épaisse. Chaussette. C'est un habit. Oui. Pose-la sur la chaise. Amir pose la chaussette sur la chaise. Il prend le gant jaune. Le gant sent la laine. Gant. C'est un habit. Les habits ensemble. C'est une catégorie. Amir pose le gant sur la chaise. Catégorie. Fruits. Habits. Bravo, Amir. Tu as nommé. Tu as classé. Tu as mis ensemble. C'est du bon travail. Tu as fini de ranger le panier ? Oui, papa. Le panier a les fruits. La chaise a les habits. Le grain près du sel attend encore. On le met avec le raisin ? Oui. C'est un fruit. Amir pose le grain avec la grappe. L'horloge fait tac, tout calme.</t>
+          <t>Un grain de raisin roule, tout seul. Il s'arrête près du sel. Les volets laissent un filet d'or. L'horloge fait tic, puis tac. L'évier sent encore le savon. Une chaise racle un tout petit peu. Amir, tu as vu le grain ? Il a fait la course. Oui, papa. Il est tout rond. Le panier s'est mélangé, lui aussi. Viens voir. En ce moment, Amir monte sur la chaise. Le bois est lisse sous les mains. Papa pose le panier sur la table. Dedans, il y a une poire. Un raisin. Une chaussette. Un gant. La poire est lisse. Touche. Elle est froide. Amir touche la poire verte. Elle sent un peu l'herbe. Et le gant ? Il est jaune. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Amir prend la poire. Poire. C'est un fruit. Oui. Mets-la dans le panier. Amir met la poire dans le panier. Il prend la grappe de raisin. Les grains sont lisses et froids. Raisin. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Amir met le raisin avec la poire. Il prend la chaussette bleue. Elle est douce, un peu épaisse. Chaussette. C'est un habit. Oui. Pose-la sur la chaise. Amir pose la chaussette sur la chaise. Il prend le gant jaune. Le gant sent la laine. Gant. C'est un habit. Les habits ensemble. C'est une catégorie. Amir pose le gant sur la chaise. Catégorie. Fruits. Habits. Bravo, Amir. Tu as nommé. Tu as classé. Tu as mis ensemble. Tu as fini de ranger le panier ? Oui, papa. Le panier a les fruits. La chaise a les habits. Le grain près du sel attend encore. On le met avec le raisin ? Oui. C'est un fruit. Amir pose le grain avec la grappe. L'horloge fait tac, tout calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nassim est dans la cuisine. Papa pose un panier. Dedans, il y a une poire. Un raisin. Une chaussette. Un gant. Nassim touche la poire. Elle est lisse. Papa dit : on nomme. On classe. Les fruits ensemble. Les habits ensemble. La poire, c'est un fruit. Le raisin, c'est un fruit. Nassim les met ensemble. La chaussette, c'est un habit. Le gant, c'est un habit. Nassim les met ensemble. Papa dit : fruits, c'est une &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt;. Habits, c'est une catégorie. Nassim répète : catégorie. Il pose les fruits dans le panier. Il pose les habits sur la chaise.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un grain de raisin roule, tout seul. Il s'arrête près du sel. Les volets laissent un filet d'or. L'horloge fait tic, puis tac. L'évier sent encore le savon. Une chaise racle un tout petit peu. Amir, tu as vu le grain ? Il a fait la course. Oui, papa. Il est tout rond. Le panier s'est mélangé, lui aussi. Viens voir. En ce moment, Amir monte sur la chaise. Le bois est lisse sous les mains. Papa pose le panier sur la table. Dedans, il y a une poire. Un raisin. Une chaussette. Un gant. La poire est lisse. Touche. Elle est froide. Amir touche la poire verte. Elle sent un peu l'herbe. Et le gant ? Il est jaune. On nomme. On classe. Les fruits ensemble. Les habits ensemble. Amir prend la poire. Poire. C'est un fruit. Oui. Mets-la dans le panier. Amir met la poire dans le panier. Il prend la grappe de raisin. Les grains sont lisses et froids. Raisin. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Amir met le raisin avec la poire. Il prend la chaussette bleue. Elle est douce, un peu épaisse. Chaussette. C'est un habit. Oui. Pose-la sur la chaise. Amir pose la chaussette sur la chaise. Il prend le gant jaune. Le gant sent la laine. Gant. C'est un habit. Les habits ensemble. C'est une catégorie. Amir pose le gant sur la chaise. Catégorie. Fruits. Habits. Bravo, Amir. Tu as nommé. Tu as classé. Tu as mis ensemble. Tu as fini de ranger le panier ? Oui, papa. Le panier a les fruits. La chaise a les habits. Le grain près du sel attend encore. On le met avec le raisin ? Oui. C'est un fruit. Amir pose le grain avec la grappe. L'horloge fait tac, tout calme.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1388,7 +1388,6 @@
 papa|Tu as nommé.
 papa|Tu as classé.
 papa|Tu as mis ensemble.
-papa|C'est du bon travail.
 papa|Tu as fini de ranger le panier ?
 enfant-m|Oui, papa.
 narrateur|Le panier a les fruits.
@@ -1401,7 +1400,6 @@
 narrateur|L'horloge fait tac, tout calme.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1431,7 +1429,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nassim range poire et chaussette. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir range poire et chaussette. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1586,7 +1584,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1611,12 +1608,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo, Amir. C'est du bon travail. Les fruits sont où ? Dans le panier. Et les habits ? Sur la chaise. Le filet d'or a bougé sur la table. Le savon sent encore, tout près.</t>
+          <t>Amir a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo, Amir. Les fruits sont où ? Dans le panier. Et les habits ? Sur la chaise. Le filet d'or a bougé sur la table. Le savon sent encore, tout près.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nassim a nommé. Il a classé. Une &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt; pour les fruits. Une catégorie pour les habits.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a nommé. Il a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo, Amir. Les fruits sont où ? Dans le panier. Et les habits ? Sur la chaise. Le filet d'or a bougé sur la table. Le savon sent encore, tout près.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1761,7 +1758,6 @@
 narrateur|Une catégorie pour les habits.
 papa|Tu as mis ensemble.
 papa|Bravo, Amir.
-papa|C'est du bon travail.
 papa|Les fruits sont où ?
 enfant-m|Dans le panier.
 papa|Et les habits ?
@@ -1770,7 +1766,6 @@
 narrateur|Le savon sent encore, tout près.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1800,7 +1795,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nassim croque la poire. Papa plie le gant.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir croque la poire. Elle est juteuse, un peu ferme. Tu aimes ? Oui, papa. Papa plie le gant jaune. Il pose la chaussette sur le dossier. Les habits sont ensemble. Les fruits aussi. On laisse un grain pour plus tard ? Oui. Le raisin brille dans le panier. L'horloge continue, tout doux. Tu as classé, puis tu croques. C'était bien.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1947,7 +1942,6 @@
 enfant-m|C'était bien.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1972,12 +1966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai nommé. J'ai classé. Bravo. Tu as fait du bon travail. Le grain a rejoint sa grappe. L'histoire est finie.</t>
+          <t>J'ai nommé. J'ai classé. Bravo. Le grain a rejoint sa grappe.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai nommé. J'ai classé. Bravo. Le grain a rejoint sa grappe.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2115,12 +2109,9 @@
           <t>enfant-m|J'ai nommé.
 enfant-m|J'ai classé.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Le grain a rejoint sa grappe.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le grain a rejoint sa grappe.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2139,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2184,6 +2175,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-03.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nassim, papa</t>
+          <t>Amir, papa</t>
         </is>
       </c>
     </row>
